--- a/artfynd/A 34582-2024 artfynd.xlsx
+++ b/artfynd/A 34582-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875870</v>
+        <v>119875885</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467191</v>
+        <v>467181</v>
       </c>
       <c r="R2" t="n">
-        <v>7052736</v>
+        <v>7052992</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875867</v>
+        <v>119875869</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467063</v>
+        <v>467150</v>
       </c>
       <c r="R3" t="n">
-        <v>7052669</v>
+        <v>7052611</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875868</v>
+        <v>119875867</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467112</v>
+        <v>467063</v>
       </c>
       <c r="R4" t="n">
-        <v>7052617</v>
+        <v>7052669</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875877</v>
+        <v>119875864</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467236</v>
+        <v>466974</v>
       </c>
       <c r="R5" t="n">
-        <v>7053152</v>
+        <v>7052798</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875869</v>
+        <v>119875863</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467150</v>
+        <v>466980</v>
       </c>
       <c r="R6" t="n">
-        <v>7052611</v>
+        <v>7052811</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119875866</v>
+        <v>119875870</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466936</v>
+        <v>467191</v>
       </c>
       <c r="R7" t="n">
-        <v>7052763</v>
+        <v>7052736</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119875871</v>
+        <v>119875877</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467248</v>
+        <v>467236</v>
       </c>
       <c r="R8" t="n">
-        <v>7052760</v>
+        <v>7053152</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119875830</v>
+        <v>119875868</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467065</v>
+        <v>467112</v>
       </c>
       <c r="R9" t="n">
-        <v>7052907</v>
+        <v>7052617</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119875864</v>
+        <v>119875866</v>
       </c>
       <c r="B10" t="n">
         <v>57310</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466974</v>
+        <v>466936</v>
       </c>
       <c r="R10" t="n">
-        <v>7052798</v>
+        <v>7052763</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119875885</v>
+        <v>119875871</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467181</v>
+        <v>467248</v>
       </c>
       <c r="R11" t="n">
-        <v>7052992</v>
+        <v>7052760</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1709,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119875863</v>
+        <v>119875830</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466980</v>
+        <v>467065</v>
       </c>
       <c r="R12" t="n">
-        <v>7052811</v>
+        <v>7052907</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,11 +1816,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 34582-2024 artfynd.xlsx
+++ b/artfynd/A 34582-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875885</v>
+        <v>119875868</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467181</v>
+        <v>467112</v>
       </c>
       <c r="R2" t="n">
-        <v>7052992</v>
+        <v>7052617</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875869</v>
+        <v>119875866</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467150</v>
+        <v>466936</v>
       </c>
       <c r="R3" t="n">
-        <v>7052611</v>
+        <v>7052763</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875867</v>
+        <v>119875870</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467063</v>
+        <v>467191</v>
       </c>
       <c r="R4" t="n">
-        <v>7052669</v>
+        <v>7052736</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875864</v>
+        <v>119875869</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466974</v>
+        <v>467150</v>
       </c>
       <c r="R5" t="n">
-        <v>7052798</v>
+        <v>7052611</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875863</v>
+        <v>119875877</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466980</v>
+        <v>467236</v>
       </c>
       <c r="R6" t="n">
-        <v>7052811</v>
+        <v>7053152</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119875870</v>
+        <v>119875871</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467191</v>
+        <v>467248</v>
       </c>
       <c r="R7" t="n">
-        <v>7052736</v>
+        <v>7052760</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119875877</v>
+        <v>119875863</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467236</v>
+        <v>466980</v>
       </c>
       <c r="R8" t="n">
-        <v>7053152</v>
+        <v>7052811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119875868</v>
+        <v>119875830</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467112</v>
+        <v>467065</v>
       </c>
       <c r="R9" t="n">
-        <v>7052617</v>
+        <v>7052907</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,11 +1500,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119875866</v>
+        <v>119875867</v>
       </c>
       <c r="B10" t="n">
         <v>57310</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466936</v>
+        <v>467063</v>
       </c>
       <c r="R10" t="n">
-        <v>7052763</v>
+        <v>7052669</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119875871</v>
+        <v>119875885</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467248</v>
+        <v>467181</v>
       </c>
       <c r="R11" t="n">
-        <v>7052760</v>
+        <v>7052992</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119875830</v>
+        <v>119875864</v>
       </c>
       <c r="B12" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467065</v>
+        <v>466974</v>
       </c>
       <c r="R12" t="n">
-        <v>7052907</v>
+        <v>7052798</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,6 +1811,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 34582-2024 artfynd.xlsx
+++ b/artfynd/A 34582-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875868</v>
+        <v>119875869</v>
       </c>
       <c r="B2" t="n">
         <v>57310</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467112</v>
+        <v>467150</v>
       </c>
       <c r="R2" t="n">
-        <v>7052617</v>
+        <v>7052611</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875866</v>
+        <v>119875871</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466936</v>
+        <v>467248</v>
       </c>
       <c r="R3" t="n">
-        <v>7052763</v>
+        <v>7052760</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875870</v>
+        <v>119875863</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467191</v>
+        <v>466980</v>
       </c>
       <c r="R4" t="n">
-        <v>7052736</v>
+        <v>7052811</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875869</v>
+        <v>119875885</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467150</v>
+        <v>467181</v>
       </c>
       <c r="R5" t="n">
-        <v>7052611</v>
+        <v>7052992</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875877</v>
+        <v>119875870</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467236</v>
+        <v>467191</v>
       </c>
       <c r="R6" t="n">
-        <v>7053152</v>
+        <v>7052736</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119875871</v>
+        <v>119875830</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467248</v>
+        <v>467065</v>
       </c>
       <c r="R7" t="n">
-        <v>7052760</v>
+        <v>7052907</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119875863</v>
+        <v>119875864</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1357,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466980</v>
+        <v>466974</v>
       </c>
       <c r="R8" t="n">
-        <v>7052811</v>
+        <v>7052798</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119875830</v>
+        <v>119875866</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467065</v>
+        <v>466936</v>
       </c>
       <c r="R9" t="n">
-        <v>7052907</v>
+        <v>7052763</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1633,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119875885</v>
+        <v>119875877</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467181</v>
+        <v>467236</v>
       </c>
       <c r="R11" t="n">
-        <v>7052992</v>
+        <v>7053152</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1704,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119875864</v>
+        <v>119875868</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466974</v>
+        <v>467112</v>
       </c>
       <c r="R12" t="n">
-        <v>7052798</v>
+        <v>7052617</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 34582-2024 artfynd.xlsx
+++ b/artfynd/A 34582-2024 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875885</v>
+        <v>119875870</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467181</v>
+        <v>467191</v>
       </c>
       <c r="R5" t="n">
-        <v>7052992</v>
+        <v>7052736</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875870</v>
+        <v>119875885</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467191</v>
+        <v>467181</v>
       </c>
       <c r="R6" t="n">
-        <v>7052736</v>
+        <v>7052992</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 34582-2024 artfynd.xlsx
+++ b/artfynd/A 34582-2024 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875870</v>
+        <v>119875885</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467191</v>
+        <v>467181</v>
       </c>
       <c r="R5" t="n">
-        <v>7052736</v>
+        <v>7052992</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875885</v>
+        <v>119875870</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467181</v>
+        <v>467191</v>
       </c>
       <c r="R6" t="n">
-        <v>7052992</v>
+        <v>7052736</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 34582-2024 artfynd.xlsx
+++ b/artfynd/A 34582-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875869</v>
+        <v>119875871</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467150</v>
+        <v>467248</v>
       </c>
       <c r="R2" t="n">
-        <v>7052611</v>
+        <v>7052760</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875871</v>
+        <v>119875863</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467248</v>
+        <v>466980</v>
       </c>
       <c r="R3" t="n">
-        <v>7052760</v>
+        <v>7052811</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875863</v>
+        <v>119875830</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466980</v>
+        <v>467065</v>
       </c>
       <c r="R4" t="n">
-        <v>7052811</v>
+        <v>7052907</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875885</v>
+        <v>119875864</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467181</v>
+        <v>466974</v>
       </c>
       <c r="R5" t="n">
-        <v>7052992</v>
+        <v>7052798</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875870</v>
+        <v>119875868</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467191</v>
+        <v>467112</v>
       </c>
       <c r="R6" t="n">
-        <v>7052736</v>
+        <v>7052617</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119875830</v>
+        <v>119875867</v>
       </c>
       <c r="B7" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467065</v>
+        <v>467063</v>
       </c>
       <c r="R7" t="n">
-        <v>7052907</v>
+        <v>7052669</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119875864</v>
+        <v>119875885</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466974</v>
+        <v>467181</v>
       </c>
       <c r="R8" t="n">
-        <v>7052798</v>
+        <v>7052992</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119875866</v>
+        <v>119875877</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466936</v>
+        <v>467236</v>
       </c>
       <c r="R9" t="n">
-        <v>7052763</v>
+        <v>7053152</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119875867</v>
+        <v>119875870</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467063</v>
+        <v>467191</v>
       </c>
       <c r="R10" t="n">
-        <v>7052669</v>
+        <v>7052736</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119875877</v>
+        <v>119875866</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467236</v>
+        <v>466936</v>
       </c>
       <c r="R11" t="n">
-        <v>7053152</v>
+        <v>7052763</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119875868</v>
+        <v>119875869</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467112</v>
+        <v>467150</v>
       </c>
       <c r="R12" t="n">
-        <v>7052617</v>
+        <v>7052611</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 34582-2024 artfynd.xlsx
+++ b/artfynd/A 34582-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875871</v>
+        <v>119875867</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467248</v>
+        <v>467063</v>
       </c>
       <c r="R2" t="n">
-        <v>7052760</v>
+        <v>7052669</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875863</v>
+        <v>119875864</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466980</v>
+        <v>466974</v>
       </c>
       <c r="R3" t="n">
-        <v>7052811</v>
+        <v>7052798</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875830</v>
+        <v>119875868</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467065</v>
+        <v>467112</v>
       </c>
       <c r="R4" t="n">
-        <v>7052907</v>
+        <v>7052617</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875864</v>
+        <v>119875871</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466974</v>
+        <v>467248</v>
       </c>
       <c r="R5" t="n">
-        <v>7052798</v>
+        <v>7052760</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875868</v>
+        <v>119875877</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467112</v>
+        <v>467236</v>
       </c>
       <c r="R6" t="n">
-        <v>7052617</v>
+        <v>7053152</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119875867</v>
+        <v>119875885</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467063</v>
+        <v>467181</v>
       </c>
       <c r="R7" t="n">
-        <v>7052669</v>
+        <v>7052992</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119875885</v>
+        <v>119875863</v>
       </c>
       <c r="B8" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467181</v>
+        <v>466980</v>
       </c>
       <c r="R8" t="n">
-        <v>7052992</v>
+        <v>7052811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1388,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119875877</v>
+        <v>119875870</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1454,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467236</v>
+        <v>467191</v>
       </c>
       <c r="R9" t="n">
-        <v>7053152</v>
+        <v>7052736</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119875870</v>
+        <v>119875830</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467191</v>
+        <v>467065</v>
       </c>
       <c r="R10" t="n">
-        <v>7052736</v>
+        <v>7052907</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 34582-2024 artfynd.xlsx
+++ b/artfynd/A 34582-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875867</v>
+        <v>119875868</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467063</v>
+        <v>467112</v>
       </c>
       <c r="R2" t="n">
-        <v>7052669</v>
+        <v>7052617</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875864</v>
+        <v>119875866</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466974</v>
+        <v>466936</v>
       </c>
       <c r="R3" t="n">
-        <v>7052798</v>
+        <v>7052763</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875868</v>
+        <v>119875869</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467112</v>
+        <v>467150</v>
       </c>
       <c r="R4" t="n">
-        <v>7052617</v>
+        <v>7052611</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875871</v>
+        <v>119875867</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467248</v>
+        <v>467063</v>
       </c>
       <c r="R5" t="n">
-        <v>7052760</v>
+        <v>7052669</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875877</v>
+        <v>119875885</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467236</v>
+        <v>467181</v>
       </c>
       <c r="R6" t="n">
-        <v>7053152</v>
+        <v>7052992</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119875885</v>
+        <v>119875830</v>
       </c>
       <c r="B7" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467181</v>
+        <v>467065</v>
       </c>
       <c r="R7" t="n">
-        <v>7052992</v>
+        <v>7052907</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119875863</v>
+        <v>119875871</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466980</v>
+        <v>467248</v>
       </c>
       <c r="R8" t="n">
-        <v>7052811</v>
+        <v>7052760</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119875870</v>
+        <v>119875863</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1459,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467191</v>
+        <v>466980</v>
       </c>
       <c r="R9" t="n">
-        <v>7052736</v>
+        <v>7052811</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119875830</v>
+        <v>119875864</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467065</v>
+        <v>466974</v>
       </c>
       <c r="R10" t="n">
-        <v>7052907</v>
+        <v>7052798</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,6 +1597,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119875866</v>
+        <v>119875877</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466936</v>
+        <v>467236</v>
       </c>
       <c r="R11" t="n">
-        <v>7052763</v>
+        <v>7053152</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119875869</v>
+        <v>119875870</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467150</v>
+        <v>467191</v>
       </c>
       <c r="R12" t="n">
-        <v>7052611</v>
+        <v>7052736</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 34582-2024 artfynd.xlsx
+++ b/artfynd/A 34582-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875868</v>
+        <v>119875869</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467112</v>
+        <v>467150</v>
       </c>
       <c r="R2" t="n">
-        <v>7052617</v>
+        <v>7052611</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875866</v>
+        <v>119875830</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466936</v>
+        <v>467065</v>
       </c>
       <c r="R3" t="n">
-        <v>7052763</v>
+        <v>7052907</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875869</v>
+        <v>119875866</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467150</v>
+        <v>466936</v>
       </c>
       <c r="R4" t="n">
-        <v>7052611</v>
+        <v>7052763</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875867</v>
+        <v>119875870</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467063</v>
+        <v>467191</v>
       </c>
       <c r="R5" t="n">
-        <v>7052669</v>
+        <v>7052736</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875885</v>
+        <v>119875867</v>
       </c>
       <c r="B6" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467181</v>
+        <v>467063</v>
       </c>
       <c r="R6" t="n">
-        <v>7052992</v>
+        <v>7052669</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119875830</v>
+        <v>119875864</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467065</v>
+        <v>466974</v>
       </c>
       <c r="R7" t="n">
-        <v>7052907</v>
+        <v>7052798</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119875871</v>
+        <v>119875863</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467248</v>
+        <v>466980</v>
       </c>
       <c r="R8" t="n">
-        <v>7052760</v>
+        <v>7052811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119875863</v>
+        <v>119875871</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1454,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466980</v>
+        <v>467248</v>
       </c>
       <c r="R9" t="n">
-        <v>7052811</v>
+        <v>7052760</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119875864</v>
+        <v>119875885</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466974</v>
+        <v>467181</v>
       </c>
       <c r="R10" t="n">
-        <v>7052798</v>
+        <v>7052992</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119875877</v>
+        <v>119875868</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467236</v>
+        <v>467112</v>
       </c>
       <c r="R11" t="n">
-        <v>7053152</v>
+        <v>7052617</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119875870</v>
+        <v>119875877</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467191</v>
+        <v>467236</v>
       </c>
       <c r="R12" t="n">
-        <v>7052736</v>
+        <v>7053152</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 34582-2024 artfynd.xlsx
+++ b/artfynd/A 34582-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875869</v>
+        <v>119875885</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467150</v>
+        <v>467181</v>
       </c>
       <c r="R2" t="n">
-        <v>7052611</v>
+        <v>7052992</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875830</v>
+        <v>119875869</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467065</v>
+        <v>467150</v>
       </c>
       <c r="R3" t="n">
-        <v>7052907</v>
+        <v>7052611</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875866</v>
+        <v>119875830</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466936</v>
+        <v>467065</v>
       </c>
       <c r="R4" t="n">
-        <v>7052763</v>
+        <v>7052907</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1098,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875867</v>
+        <v>119875868</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467063</v>
+        <v>467112</v>
       </c>
       <c r="R6" t="n">
-        <v>7052669</v>
+        <v>7052617</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119875864</v>
+        <v>119875863</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466974</v>
+        <v>466980</v>
       </c>
       <c r="R7" t="n">
-        <v>7052798</v>
+        <v>7052811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119875863</v>
+        <v>119875871</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466980</v>
+        <v>467248</v>
       </c>
       <c r="R8" t="n">
-        <v>7052811</v>
+        <v>7052760</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119875871</v>
+        <v>119875864</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1459,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467248</v>
+        <v>466974</v>
       </c>
       <c r="R9" t="n">
-        <v>7052760</v>
+        <v>7052798</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119875885</v>
+        <v>119875877</v>
       </c>
       <c r="B10" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467181</v>
+        <v>467236</v>
       </c>
       <c r="R10" t="n">
-        <v>7052992</v>
+        <v>7053152</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,6 +1597,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119875868</v>
+        <v>119875867</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467112</v>
+        <v>467063</v>
       </c>
       <c r="R11" t="n">
-        <v>7052617</v>
+        <v>7052669</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119875877</v>
+        <v>119875866</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467236</v>
+        <v>466936</v>
       </c>
       <c r="R12" t="n">
-        <v>7053152</v>
+        <v>7052763</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 34582-2024 artfynd.xlsx
+++ b/artfynd/A 34582-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875885</v>
+        <v>119875830</v>
       </c>
       <c r="B2" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467181</v>
+        <v>467065</v>
       </c>
       <c r="R2" t="n">
-        <v>7052992</v>
+        <v>7052907</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875869</v>
+        <v>119875862</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467150</v>
+        <v>466963</v>
       </c>
       <c r="R3" t="n">
-        <v>7052611</v>
+        <v>7052872</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,15 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875830</v>
+        <v>119875863</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467065</v>
+        <v>466980</v>
       </c>
       <c r="R4" t="n">
-        <v>7052907</v>
+        <v>7052811</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875870</v>
+        <v>119875864</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467191</v>
+        <v>466974</v>
       </c>
       <c r="R5" t="n">
-        <v>7052736</v>
+        <v>7052798</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,15 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875868</v>
+        <v>119875866</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467112</v>
+        <v>466936</v>
       </c>
       <c r="R6" t="n">
-        <v>7052617</v>
+        <v>7052763</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119875863</v>
+        <v>119875867</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466980</v>
+        <v>467063</v>
       </c>
       <c r="R7" t="n">
-        <v>7052811</v>
+        <v>7052669</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,15 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119875871</v>
+        <v>119875868</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467248</v>
+        <v>467112</v>
       </c>
       <c r="R8" t="n">
-        <v>7052760</v>
+        <v>7052617</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,15 +1384,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119875864</v>
+        <v>119875869</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466974</v>
+        <v>467150</v>
       </c>
       <c r="R9" t="n">
-        <v>7052798</v>
+        <v>7052611</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,15 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119875877</v>
+        <v>119875870</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467236</v>
+        <v>467191</v>
       </c>
       <c r="R10" t="n">
-        <v>7053152</v>
+        <v>7052736</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,15 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119875867</v>
+        <v>119875871</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467063</v>
+        <v>467248</v>
       </c>
       <c r="R11" t="n">
-        <v>7052669</v>
+        <v>7052760</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,15 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119875866</v>
+        <v>119875876</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466936</v>
+        <v>467110</v>
       </c>
       <c r="R12" t="n">
-        <v>7052763</v>
+        <v>7053045</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1765,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1839,6 +1789,108 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>119875877</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sandlingsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>467236</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7053152</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34582-2024 artfynd.xlsx
+++ b/artfynd/A 34582-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875830</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875862</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875863</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875864</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875866</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875867</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875868</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875869</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875870</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875871</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1844,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875876</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1891,8 +1951,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875877</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>